--- a/student-billing/tests/fixtures/conforming-erp-fixture.xlsx
+++ b/student-billing/tests/fixtures/conforming-erp-fixture.xlsx
@@ -8382,7 +8382,7 @@
       </c>
       <c t="inlineStr" r="I205" s="67">
         <is>
-          <t xml:space="preserve">(弟弟園內幼幼班) 匿名備註_204</t>
+          <t xml:space="preserve">園內生 (弟弟園內幼幼班) 匿名備註_204</t>
         </is>
       </c>
     </row>
